--- a/output/yearly_benthic_cover_iteration_31_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_31_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.40564399344738</v>
+        <v>45.183302305254</v>
       </c>
       <c r="M2" t="n">
-        <v>99.15211211405486</v>
+        <v>99.5586506016555</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.9874937216974</v>
+        <v>88.02610585890542</v>
       </c>
       <c r="C3" t="n">
-        <v>45.89653185873543</v>
+        <v>45.91154482644109</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228652832744707</v>
+        <v>2.228740528272779</v>
       </c>
       <c r="E3" t="n">
-        <v>5.685858373338578</v>
+        <v>5.6965547893054</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428842775815689</v>
+        <v>0.7429135094242599</v>
       </c>
       <c r="G3" t="n">
-        <v>33.96236940805532</v>
+        <v>33.96717478562327</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17267676875217</v>
+        <v>34.17402143351595</v>
       </c>
       <c r="I3" t="n">
-        <v>6.552025326340268</v>
+        <v>6.573491378862144</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643026734884806</v>
+        <v>4.643209433901625</v>
       </c>
       <c r="K3" t="n">
-        <v>12.01250627830258</v>
+        <v>11.97389414109456</v>
       </c>
       <c r="L3" t="n">
-        <v>48.85576954480192</v>
+        <v>48.87860745077197</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7648076818399</v>
+        <v>106.7640464183076</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.08347239018127</v>
+        <v>87.07165914900202</v>
       </c>
       <c r="C4" t="n">
-        <v>42.62574707775126</v>
+        <v>42.59392181645314</v>
       </c>
       <c r="D4" t="n">
-        <v>2.185108349987969</v>
+        <v>2.182539549603782</v>
       </c>
       <c r="E4" t="n">
-        <v>6.486674727464639</v>
+        <v>6.493370832708246</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444401253540147</v>
+        <v>0.7444747389033246</v>
       </c>
       <c r="G4" t="n">
-        <v>33.29879642470927</v>
+        <v>33.26304763497068</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24424576628467</v>
+        <v>34.24583798955293</v>
       </c>
       <c r="I4" t="n">
-        <v>5.47145621291811</v>
+        <v>5.489421285117278</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652750783462592</v>
+        <v>4.652967118145779</v>
       </c>
       <c r="K4" t="n">
-        <v>12.91652760981875</v>
+        <v>12.92834085099798</v>
       </c>
       <c r="L4" t="n">
-        <v>44.27572460892053</v>
+        <v>44.2951403498027</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81799929649054</v>
+        <v>99.81740301725382</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.88253760961086</v>
+        <v>85.92848636007389</v>
       </c>
       <c r="C5" t="n">
-        <v>42.27400932096192</v>
+        <v>42.30267959019088</v>
       </c>
       <c r="D5" t="n">
-        <v>2.126347213413549</v>
+        <v>2.126821991936931</v>
       </c>
       <c r="E5" t="n">
-        <v>7.073509120990777</v>
+        <v>7.091378015544648</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457598841862673</v>
+        <v>0.7457981909962211</v>
       </c>
       <c r="G5" t="n">
-        <v>32.40333733935685</v>
+        <v>32.41388282826045</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30495467256829</v>
+        <v>34.30671678582617</v>
       </c>
       <c r="I5" t="n">
-        <v>4.567630102930969</v>
+        <v>4.582649853783077</v>
       </c>
       <c r="J5" t="n">
-        <v>4.66099927616417</v>
+        <v>4.661238693726382</v>
       </c>
       <c r="K5" t="n">
-        <v>14.11746239038911</v>
+        <v>14.07151363992609</v>
       </c>
       <c r="L5" t="n">
-        <v>43.45654339384569</v>
+        <v>43.47332284529644</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84801510519672</v>
+        <v>99.84751607541342</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.40241786422152</v>
+        <v>84.62754178144237</v>
       </c>
       <c r="C6" t="n">
-        <v>41.50322688240959</v>
+        <v>41.71341559446547</v>
       </c>
       <c r="D6" t="n">
-        <v>2.053785378553048</v>
+        <v>2.063465610756509</v>
       </c>
       <c r="E6" t="n">
-        <v>7.467472998574382</v>
+        <v>7.517569326154467</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468826415284571</v>
+        <v>0.7469217025093828</v>
       </c>
       <c r="G6" t="n">
-        <v>31.29756985316491</v>
+        <v>31.44829834409094</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35660151030902</v>
+        <v>34.35839831543161</v>
       </c>
       <c r="I6" t="n">
-        <v>3.812088972538847</v>
+        <v>3.824627841815827</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668016509552857</v>
+        <v>4.668260640683643</v>
       </c>
       <c r="K6" t="n">
-        <v>15.59758213577849</v>
+        <v>15.37245821855763</v>
       </c>
       <c r="L6" t="n">
-        <v>42.77231236784159</v>
+        <v>42.78683035770511</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87312138602968</v>
+        <v>99.87270417072821</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.74880210842521</v>
+        <v>83.06358030396417</v>
       </c>
       <c r="C7" t="n">
-        <v>40.44155191776599</v>
+        <v>40.74349181739642</v>
       </c>
       <c r="D7" t="n">
-        <v>1.973109200929339</v>
+        <v>1.987352014827688</v>
       </c>
       <c r="E7" t="n">
-        <v>7.704273178283533</v>
+        <v>7.772152658342518</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478396312837317</v>
+        <v>0.7478782508847877</v>
       </c>
       <c r="G7" t="n">
-        <v>30.06814815651067</v>
+        <v>30.28828721507891</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40062303905165</v>
+        <v>34.40239954070023</v>
       </c>
       <c r="I7" t="n">
-        <v>3.180811206842964</v>
+        <v>3.191271556100117</v>
       </c>
       <c r="J7" t="n">
-        <v>4.673997695523322</v>
+        <v>4.674239068029923</v>
       </c>
       <c r="K7" t="n">
-        <v>17.2511978915748</v>
+        <v>16.93641969603582</v>
       </c>
       <c r="L7" t="n">
-        <v>42.20135883031092</v>
+        <v>42.21384882429511</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89410863965171</v>
+        <v>99.89376033772734</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.64004115969482</v>
+        <v>87.77884154389709</v>
       </c>
       <c r="C8" t="n">
-        <v>42.77158555792312</v>
+        <v>42.95930324481424</v>
       </c>
       <c r="D8" t="n">
-        <v>1.977325972909014</v>
+        <v>1.991555137121476</v>
       </c>
       <c r="E8" t="n">
-        <v>9.554956482685046</v>
+        <v>9.543474015864252</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494378546365</v>
+        <v>0.7494599655110237</v>
       </c>
       <c r="G8" t="n">
-        <v>30.58127327691972</v>
+        <v>30.76567030270026</v>
       </c>
       <c r="H8" t="n">
-        <v>34.474141313279</v>
+        <v>34.47515841350709</v>
       </c>
       <c r="I8" t="n">
-        <v>5.618919667787408</v>
+        <v>5.569398924749087</v>
       </c>
       <c r="J8" t="n">
-        <v>4.683986591478125</v>
+        <v>4.684124784443899</v>
       </c>
       <c r="K8" t="n">
-        <v>12.35995884030517</v>
+        <v>12.22115845610291</v>
       </c>
       <c r="L8" t="n">
-        <v>44.68155770282989</v>
+        <v>44.63428347036179</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81310210105819</v>
+        <v>99.81474517127894</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.54148502083622</v>
+        <v>85.68677256624883</v>
       </c>
       <c r="C9" t="n">
-        <v>41.54484295770661</v>
+        <v>41.73161807198613</v>
       </c>
       <c r="D9" t="n">
-        <v>1.882228411963174</v>
+        <v>1.896482696582608</v>
       </c>
       <c r="E9" t="n">
-        <v>9.877252244692865</v>
+        <v>9.862816400303597</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508077970479163</v>
+        <v>0.7508155459612321</v>
       </c>
       <c r="G9" t="n">
-        <v>29.11049681461758</v>
+        <v>29.29698520030358</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53715866420415</v>
+        <v>34.53751511421667</v>
       </c>
       <c r="I9" t="n">
-        <v>4.69099235676106</v>
+        <v>4.649560446623436</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692548731549477</v>
+        <v>4.692597162257702</v>
       </c>
       <c r="K9" t="n">
-        <v>14.45851497916376</v>
+        <v>14.31322743375118</v>
       </c>
       <c r="L9" t="n">
-        <v>43.84056096124663</v>
+        <v>43.80044896857522</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84391889811701</v>
+        <v>99.84529447431252</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.20944740526609</v>
+        <v>83.35141251684099</v>
       </c>
       <c r="C10" t="n">
-        <v>39.94027436896821</v>
+        <v>40.11751207799642</v>
       </c>
       <c r="D10" t="n">
-        <v>1.777612337711243</v>
+        <v>1.791382908988196</v>
       </c>
       <c r="E10" t="n">
-        <v>9.980813621096305</v>
+        <v>9.963010663752021</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519854002979727</v>
+        <v>0.7519807531581307</v>
       </c>
       <c r="G10" t="n">
-        <v>27.49250726727447</v>
+        <v>27.67339700345002</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59132841370674</v>
+        <v>34.59111464527401</v>
       </c>
       <c r="I10" t="n">
-        <v>3.915291613317037</v>
+        <v>3.880646834980292</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699908751862329</v>
+        <v>4.699879707238318</v>
       </c>
       <c r="K10" t="n">
-        <v>16.7905525947339</v>
+        <v>16.64858748315902</v>
       </c>
       <c r="L10" t="n">
-        <v>43.13886769305451</v>
+        <v>43.1047459819939</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86969465675662</v>
+        <v>99.87084554314934</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>80.74984380763254</v>
+        <v>80.93860908143537</v>
       </c>
       <c r="C11" t="n">
-        <v>38.08710553059602</v>
+        <v>38.30594662102334</v>
       </c>
       <c r="D11" t="n">
-        <v>1.668467982423497</v>
+        <v>1.684001120857983</v>
       </c>
       <c r="E11" t="n">
-        <v>9.912521411726535</v>
+        <v>9.905490292989002</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7529995793969398</v>
+        <v>0.752983592576414</v>
       </c>
       <c r="G11" t="n">
-        <v>25.80448344044065</v>
+        <v>26.0145563173199</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63798065225923</v>
+        <v>34.63724525851504</v>
       </c>
       <c r="I11" t="n">
-        <v>3.267143370154828</v>
+        <v>3.238185045574434</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706247371230874</v>
+        <v>4.706147453602588</v>
       </c>
       <c r="K11" t="n">
-        <v>19.25015619236745</v>
+        <v>19.06139091856464</v>
       </c>
       <c r="L11" t="n">
-        <v>42.55398017666661</v>
+        <v>42.5248667149959</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89124189963007</v>
+        <v>99.89220425458389</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.22016725526848</v>
+        <v>78.50210077644212</v>
       </c>
       <c r="C12" t="n">
-        <v>36.06256577414503</v>
+        <v>36.37027094174651</v>
       </c>
       <c r="D12" t="n">
-        <v>1.557378537354196</v>
+        <v>1.576694941553771</v>
       </c>
       <c r="E12" t="n">
-        <v>9.706825828044311</v>
+        <v>9.724566722202143</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538742526831166</v>
+        <v>0.7538473689214427</v>
       </c>
       <c r="G12" t="n">
-        <v>24.08637690444666</v>
+        <v>24.35688364113807</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67821562342336</v>
+        <v>34.67697897038637</v>
       </c>
       <c r="I12" t="n">
-        <v>2.72578203004735</v>
+        <v>2.701583076481314</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711714079269479</v>
+        <v>4.711546055759017</v>
       </c>
       <c r="K12" t="n">
-        <v>21.77983274473154</v>
+        <v>21.49789922355789</v>
       </c>
       <c r="L12" t="n">
-        <v>42.06684749861913</v>
+        <v>42.04188025009633</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90924601749569</v>
+        <v>99.91005041540072</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>75.61133760117922</v>
+        <v>76.12936227143203</v>
       </c>
       <c r="C13" t="n">
-        <v>33.87420670594562</v>
+        <v>34.41447404053885</v>
       </c>
       <c r="D13" t="n">
-        <v>1.443891800062359</v>
+        <v>1.473231875328622</v>
       </c>
       <c r="E13" t="n">
-        <v>9.378446242408582</v>
+        <v>9.462028638211496</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546299288542749</v>
+        <v>0.7545912018014336</v>
       </c>
       <c r="G13" t="n">
-        <v>22.33119390782531</v>
+        <v>22.75857961999501</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71297672729665</v>
+        <v>34.71119528286594</v>
       </c>
       <c r="I13" t="n">
-        <v>2.273761939392822</v>
+        <v>2.253540641970553</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716437055339219</v>
+        <v>4.71619501125896</v>
       </c>
       <c r="K13" t="n">
-        <v>24.38866239882078</v>
+        <v>23.87063772856797</v>
       </c>
       <c r="L13" t="n">
-        <v>41.6614147277323</v>
+        <v>41.63984425654647</v>
       </c>
       <c r="M13" t="n">
-        <v>99.9242838324987</v>
+        <v>99.9249560256533</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>82.85083110221672</v>
+        <v>83.14850682362137</v>
       </c>
       <c r="C14" t="n">
-        <v>38.44890626415727</v>
+        <v>38.81189875988029</v>
       </c>
       <c r="D14" t="n">
-        <v>1.445546037563355</v>
+        <v>1.474929470610393</v>
       </c>
       <c r="E14" t="n">
-        <v>11.89946553449133</v>
+        <v>11.89670805743143</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7554944930325813</v>
+        <v>0.7554607122195124</v>
       </c>
       <c r="G14" t="n">
-        <v>24.39245032984274</v>
+        <v>24.72952321216636</v>
       </c>
       <c r="H14" t="n">
-        <v>36.78841870634007</v>
+        <v>36.69591179449002</v>
       </c>
       <c r="I14" t="n">
-        <v>2.847615419493009</v>
+        <v>2.874344125331722</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721840581453633</v>
+        <v>4.721629451371952</v>
       </c>
       <c r="K14" t="n">
-        <v>17.14916889778328</v>
+        <v>16.85149317637861</v>
       </c>
       <c r="L14" t="n">
-        <v>44.30711294813241</v>
+        <v>44.24090686874655</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90518811007297</v>
+        <v>99.90429880500545</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>81.99166441632217</v>
+        <v>82.43233169085036</v>
       </c>
       <c r="C15" t="n">
-        <v>38.02929185063171</v>
+        <v>38.53966078150832</v>
       </c>
       <c r="D15" t="n">
-        <v>1.413999509986261</v>
+        <v>1.448608804599516</v>
       </c>
       <c r="E15" t="n">
-        <v>12.03566446545872</v>
+        <v>12.08400837975351</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562240506862822</v>
+        <v>0.7561931511441373</v>
       </c>
       <c r="G15" t="n">
-        <v>23.86012753485217</v>
+        <v>24.28821565540143</v>
       </c>
       <c r="H15" t="n">
-        <v>36.82394414389427</v>
+        <v>36.73148944100181</v>
       </c>
       <c r="I15" t="n">
-        <v>2.375304394655209</v>
+        <v>2.397609064299107</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726400316789263</v>
+        <v>4.726207194650859</v>
       </c>
       <c r="K15" t="n">
-        <v>18.00833558367784</v>
+        <v>17.56766830914961</v>
       </c>
       <c r="L15" t="n">
-        <v>43.88327213737121</v>
+        <v>43.81282801697174</v>
       </c>
       <c r="M15" t="n">
-        <v>99.92089957168075</v>
+        <v>99.92015710762968</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>79.40338476884588</v>
+        <v>80.06528888852611</v>
       </c>
       <c r="C16" t="n">
-        <v>35.8076393016537</v>
+        <v>36.54298444750476</v>
       </c>
       <c r="D16" t="n">
-        <v>1.317000965603191</v>
+        <v>1.359077140890133</v>
       </c>
       <c r="E16" t="n">
-        <v>11.54021114278136</v>
+        <v>11.67043142204618</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7568529618017314</v>
+        <v>0.7568226946419541</v>
       </c>
       <c r="G16" t="n">
-        <v>22.22335353080915</v>
+        <v>22.78707583818103</v>
       </c>
       <c r="H16" t="n">
-        <v>36.85456864964195</v>
+        <v>36.76206902282917</v>
       </c>
       <c r="I16" t="n">
-        <v>1.981066506947665</v>
+        <v>1.999670928425436</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730331011260821</v>
+        <v>4.730141841512213</v>
       </c>
       <c r="K16" t="n">
-        <v>20.59661523115413</v>
+        <v>19.93471111147389</v>
       </c>
       <c r="L16" t="n">
-        <v>43.52976478956288</v>
+        <v>43.45570418923526</v>
       </c>
       <c r="M16" t="n">
-        <v>99.9340193223707</v>
+        <v>99.9333997482139</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.25690479950975</v>
+        <v>81.81108174360301</v>
       </c>
       <c r="C17" t="n">
-        <v>37.15531041607206</v>
+        <v>37.81958800991372</v>
       </c>
       <c r="D17" t="n">
-        <v>1.318058310031648</v>
+        <v>1.360171636677828</v>
       </c>
       <c r="E17" t="n">
-        <v>12.37204230674264</v>
+        <v>12.4681329528149</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7574605955721103</v>
+        <v>0.757432181201911</v>
       </c>
       <c r="G17" t="n">
-        <v>22.73757906830592</v>
+        <v>23.26430821515062</v>
       </c>
       <c r="H17" t="n">
-        <v>37.38054074935962</v>
+        <v>37.25055578022609</v>
       </c>
       <c r="I17" t="n">
-        <v>1.957095047172116</v>
+        <v>1.976529845019715</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734128722325689</v>
+        <v>4.733951132511944</v>
       </c>
       <c r="K17" t="n">
-        <v>18.74309520049024</v>
+        <v>18.188918256397</v>
       </c>
       <c r="L17" t="n">
-        <v>44.03641021449046</v>
+        <v>43.92566242097804</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93481583105276</v>
+        <v>99.93416868728876</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>78.86100843215769</v>
+        <v>79.55659631557063</v>
       </c>
       <c r="C18" t="n">
-        <v>35.06106266985191</v>
+        <v>35.8700775918434</v>
       </c>
       <c r="D18" t="n">
-        <v>1.232217326058</v>
+        <v>1.278382773470113</v>
       </c>
       <c r="E18" t="n">
-        <v>11.83829644806643</v>
+        <v>11.99311575908128</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7579831200319683</v>
+        <v>0.7579552613684094</v>
       </c>
       <c r="G18" t="n">
-        <v>21.25675219930713</v>
+        <v>21.86539555521714</v>
       </c>
       <c r="H18" t="n">
-        <v>37.40632723512329</v>
+        <v>37.27628089120402</v>
       </c>
       <c r="I18" t="n">
-        <v>1.632037603371066</v>
+        <v>1.648245691677115</v>
       </c>
       <c r="J18" t="n">
-        <v>4.737394500199802</v>
+        <v>4.737220383552558</v>
       </c>
       <c r="K18" t="n">
-        <v>21.13899156784232</v>
+        <v>20.44340368442937</v>
       </c>
       <c r="L18" t="n">
-        <v>43.74558201099541</v>
+        <v>43.63161511692113</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94563624868964</v>
+        <v>99.94509639319389</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>77.9556014293931</v>
+        <v>78.65762957774591</v>
       </c>
       <c r="C19" t="n">
-        <v>34.4030394113061</v>
+        <v>35.22480562404516</v>
       </c>
       <c r="D19" t="n">
-        <v>1.200271576075243</v>
+        <v>1.246401237825113</v>
       </c>
       <c r="E19" t="n">
-        <v>11.7587485097075</v>
+        <v>11.92213812933132</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7584252658615546</v>
+        <v>0.7583967047717641</v>
       </c>
       <c r="G19" t="n">
-        <v>20.70566200048898</v>
+        <v>21.31838495568988</v>
       </c>
       <c r="H19" t="n">
-        <v>37.4281470503013</v>
+        <v>37.29799110173981</v>
       </c>
       <c r="I19" t="n">
-        <v>1.364189115323821</v>
+        <v>1.374338043564507</v>
       </c>
       <c r="J19" t="n">
-        <v>4.740157911634715</v>
+        <v>4.739979404823525</v>
       </c>
       <c r="K19" t="n">
-        <v>22.0443985706069</v>
+        <v>21.34237042225409</v>
       </c>
       <c r="L19" t="n">
-        <v>43.50711555735269</v>
+        <v>43.38703935115417</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95455353926569</v>
+        <v>99.95421539745342</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>75.40068156890713</v>
+        <v>76.12078369249511</v>
       </c>
       <c r="C20" t="n">
-        <v>32.05765820210893</v>
+        <v>32.89935542619568</v>
       </c>
       <c r="D20" t="n">
-        <v>1.109736867108967</v>
+        <v>1.155295809517009</v>
       </c>
       <c r="E20" t="n">
-        <v>11.0613694894885</v>
+        <v>11.24166808906408</v>
       </c>
       <c r="F20" t="n">
-        <v>0.758806619521262</v>
+        <v>0.758777246350871</v>
       </c>
       <c r="G20" t="n">
-        <v>19.14386455353283</v>
+        <v>19.76012222834037</v>
       </c>
       <c r="H20" t="n">
-        <v>37.44696678310317</v>
+        <v>37.31670615725372</v>
       </c>
       <c r="I20" t="n">
-        <v>1.137395884144515</v>
+        <v>1.145856372276115</v>
       </c>
       <c r="J20" t="n">
-        <v>4.742541372007887</v>
+        <v>4.742357789692942</v>
       </c>
       <c r="K20" t="n">
-        <v>24.59931843109288</v>
+        <v>23.87921630750489</v>
       </c>
       <c r="L20" t="n">
-        <v>43.30512922470587</v>
+        <v>43.18325220953376</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96210585790767</v>
+        <v>99.96182394323432</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.58316901406211</v>
+        <v>81.78652823351977</v>
       </c>
       <c r="C21" t="n">
-        <v>35.96815658788134</v>
+        <v>36.438227380729</v>
       </c>
       <c r="D21" t="n">
-        <v>1.110442888246824</v>
+        <v>1.156053671850512</v>
       </c>
       <c r="E21" t="n">
-        <v>13.14659437340116</v>
+        <v>13.14550766308411</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7592893767665212</v>
+        <v>0.75927499652861</v>
       </c>
       <c r="G21" t="n">
-        <v>20.9747131027561</v>
+        <v>21.40129415685429</v>
       </c>
       <c r="H21" t="n">
-        <v>39.28945987387989</v>
+        <v>38.96939502675809</v>
       </c>
       <c r="I21" t="n">
-        <v>1.557110794220841</v>
+        <v>1.609533990140361</v>
       </c>
       <c r="J21" t="n">
-        <v>4.745558604790756</v>
+        <v>4.745468728303811</v>
       </c>
       <c r="K21" t="n">
-        <v>18.41683098593789</v>
+        <v>18.21347176648021</v>
       </c>
       <c r="L21" t="n">
-        <v>45.56314173348061</v>
+        <v>45.29468489131304</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94812930729985</v>
+        <v>99.94638403852225</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_31_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_31_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.183302305254</v>
+        <v>45.46159234493989</v>
       </c>
       <c r="M2" t="n">
-        <v>99.5586506016555</v>
+        <v>100.2823565104848</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.02610585890542</v>
+        <v>87.98650215651612</v>
       </c>
       <c r="C3" t="n">
-        <v>45.91154482644109</v>
+        <v>45.92695512925926</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228740528272779</v>
+        <v>2.22862720405282</v>
       </c>
       <c r="E3" t="n">
-        <v>5.6965547893054</v>
+        <v>5.703058544360479</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429135094242599</v>
+        <v>0.7428757346842735</v>
       </c>
       <c r="G3" t="n">
-        <v>33.96717478562327</v>
+        <v>33.97296418372759</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17402143351595</v>
+        <v>34.17228379547657</v>
       </c>
       <c r="I3" t="n">
-        <v>6.573491378862144</v>
+        <v>6.523719352437683</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643209433901625</v>
+        <v>4.642973341776709</v>
       </c>
       <c r="K3" t="n">
-        <v>11.97389414109456</v>
+        <v>12.01349784348387</v>
       </c>
       <c r="L3" t="n">
-        <v>48.87860745077197</v>
+        <v>48.82536809089375</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7640464183076</v>
+        <v>106.7658210636369</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.07165914900202</v>
+        <v>86.99453694551691</v>
       </c>
       <c r="C4" t="n">
-        <v>42.59392181645314</v>
+        <v>42.56163258810897</v>
       </c>
       <c r="D4" t="n">
-        <v>2.182539549603782</v>
+        <v>2.180413150328158</v>
       </c>
       <c r="E4" t="n">
-        <v>6.493370832708246</v>
+        <v>6.48764221814868</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444747389033246</v>
+        <v>0.7444264160345901</v>
       </c>
       <c r="G4" t="n">
-        <v>33.26304763497068</v>
+        <v>33.23799410108587</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24583798955293</v>
+        <v>34.24361513759114</v>
       </c>
       <c r="I4" t="n">
-        <v>5.489421285117278</v>
+        <v>5.447780822112297</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652967118145779</v>
+        <v>4.652665100216188</v>
       </c>
       <c r="K4" t="n">
-        <v>12.92834085099798</v>
+        <v>13.00546305448308</v>
       </c>
       <c r="L4" t="n">
-        <v>44.2951403498027</v>
+        <v>44.25168993095135</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81740301725382</v>
+        <v>99.81878557354339</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.92848636007389</v>
+        <v>85.68864042642079</v>
       </c>
       <c r="C5" t="n">
-        <v>42.30267959019088</v>
+        <v>42.10121559179454</v>
       </c>
       <c r="D5" t="n">
-        <v>2.126821991936931</v>
+        <v>2.116203306779816</v>
       </c>
       <c r="E5" t="n">
-        <v>7.091378015544648</v>
+        <v>7.054565862916278</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457981909962211</v>
+        <v>0.7457434085200632</v>
       </c>
       <c r="G5" t="n">
-        <v>32.41388282826045</v>
+        <v>32.25918584138967</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30671678582617</v>
+        <v>34.30419679192291</v>
       </c>
       <c r="I5" t="n">
-        <v>4.582649853783077</v>
+        <v>4.547848911641662</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661238693726382</v>
+        <v>4.660896303250395</v>
       </c>
       <c r="K5" t="n">
-        <v>14.07151363992609</v>
+        <v>14.3113595735792</v>
       </c>
       <c r="L5" t="n">
-        <v>43.47332284529644</v>
+        <v>43.43609758956758</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84751607541342</v>
+        <v>99.84867275494133</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.62754178144237</v>
+        <v>84.15872966871517</v>
       </c>
       <c r="C6" t="n">
-        <v>41.71341559446547</v>
+        <v>41.27743334407266</v>
       </c>
       <c r="D6" t="n">
-        <v>2.063465610756509</v>
+        <v>2.041120787132509</v>
       </c>
       <c r="E6" t="n">
-        <v>7.517569326154467</v>
+        <v>7.436866371184498</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469217025093828</v>
+        <v>0.7468645132392348</v>
       </c>
       <c r="G6" t="n">
-        <v>31.44829834409094</v>
+        <v>31.11463562403463</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35839831543161</v>
+        <v>34.35576760900479</v>
       </c>
       <c r="I6" t="n">
-        <v>3.824627841815827</v>
+        <v>3.795571556374286</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668260640683643</v>
+        <v>4.667903207745217</v>
       </c>
       <c r="K6" t="n">
-        <v>15.37245821855763</v>
+        <v>15.84127033128481</v>
       </c>
       <c r="L6" t="n">
-        <v>42.78683035770511</v>
+        <v>42.75496718820802</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87270417072821</v>
+        <v>99.87367086356551</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.06358030396417</v>
+        <v>82.38740335956614</v>
       </c>
       <c r="C7" t="n">
-        <v>40.74349181739642</v>
+        <v>40.09532370260493</v>
       </c>
       <c r="D7" t="n">
-        <v>1.987352014827688</v>
+        <v>1.954554377910416</v>
       </c>
       <c r="E7" t="n">
-        <v>7.772152658342518</v>
+        <v>7.649298044262177</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478782508847877</v>
+        <v>0.7478215129841338</v>
       </c>
       <c r="G7" t="n">
-        <v>30.28828721507891</v>
+        <v>29.79502617357656</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40239954070023</v>
+        <v>34.39978959727015</v>
       </c>
       <c r="I7" t="n">
-        <v>3.191271556100117</v>
+        <v>3.16702919741188</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674239068029923</v>
+        <v>4.673884456150836</v>
       </c>
       <c r="K7" t="n">
-        <v>16.93641969603582</v>
+        <v>17.61259664043386</v>
       </c>
       <c r="L7" t="n">
-        <v>42.21384882429511</v>
+        <v>42.18664711372858</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89376033772734</v>
+        <v>99.89456745676736</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.77884154389709</v>
+        <v>87.40878337200284</v>
       </c>
       <c r="C8" t="n">
-        <v>42.95930324481424</v>
+        <v>42.44310344583199</v>
       </c>
       <c r="D8" t="n">
-        <v>1.991555137121476</v>
+        <v>1.958813690682298</v>
       </c>
       <c r="E8" t="n">
-        <v>9.543474015864252</v>
+        <v>9.51770373840483</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494599655110237</v>
+        <v>0.7494511456806396</v>
       </c>
       <c r="G8" t="n">
-        <v>30.76567030270026</v>
+        <v>30.30962575012506</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47515841350709</v>
+        <v>34.47475270130942</v>
       </c>
       <c r="I8" t="n">
-        <v>5.569398924749087</v>
+        <v>5.714366685296601</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684124784443899</v>
+        <v>4.684069660503998</v>
       </c>
       <c r="K8" t="n">
-        <v>12.22115845610291</v>
+        <v>12.59121662799715</v>
       </c>
       <c r="L8" t="n">
-        <v>44.63428347036179</v>
+        <v>44.77561522059829</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81474517127894</v>
+        <v>99.80993529442743</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.68677256624883</v>
+        <v>85.19938211038469</v>
       </c>
       <c r="C9" t="n">
-        <v>41.73161807198613</v>
+        <v>41.11985510289921</v>
       </c>
       <c r="D9" t="n">
-        <v>1.896482696582608</v>
+        <v>1.858706241243879</v>
       </c>
       <c r="E9" t="n">
-        <v>9.862816400303597</v>
+        <v>9.826433878538857</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508155459612321</v>
+        <v>0.750850031806183</v>
       </c>
       <c r="G9" t="n">
-        <v>29.29698520030358</v>
+        <v>28.76061711203393</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53751511421667</v>
+        <v>34.53910146308441</v>
       </c>
       <c r="I9" t="n">
-        <v>4.649560446623436</v>
+        <v>4.770860684888786</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692597162257702</v>
+        <v>4.692812698788644</v>
       </c>
       <c r="K9" t="n">
-        <v>14.31322743375118</v>
+        <v>14.8006178896153</v>
       </c>
       <c r="L9" t="n">
-        <v>43.80044896857522</v>
+        <v>43.92079459956059</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84529447431252</v>
+        <v>99.8412675920751</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.35141251684099</v>
+        <v>82.83438129197826</v>
       </c>
       <c r="C10" t="n">
-        <v>40.11751207799642</v>
+        <v>39.49422598478428</v>
       </c>
       <c r="D10" t="n">
-        <v>1.791382908988196</v>
+        <v>1.752825659474122</v>
       </c>
       <c r="E10" t="n">
-        <v>9.963010663752021</v>
+        <v>9.930355687268875</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519807531581307</v>
+        <v>0.7520532161555974</v>
       </c>
       <c r="G10" t="n">
-        <v>27.67339700345002</v>
+        <v>27.12227814038368</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59111464527401</v>
+        <v>34.59444794315748</v>
       </c>
       <c r="I10" t="n">
-        <v>3.880646834980292</v>
+        <v>3.982088044566027</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699879707238318</v>
+        <v>4.700332600972484</v>
       </c>
       <c r="K10" t="n">
-        <v>16.64858748315902</v>
+        <v>17.16561870802175</v>
       </c>
       <c r="L10" t="n">
-        <v>43.1047459819939</v>
+        <v>43.20763139928038</v>
       </c>
       <c r="M10" t="n">
-        <v>99.87084554314934</v>
+        <v>99.86747609208641</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>80.93860908143537</v>
+        <v>80.3932903115298</v>
       </c>
       <c r="C11" t="n">
-        <v>38.30594662102334</v>
+        <v>37.66948950680134</v>
       </c>
       <c r="D11" t="n">
-        <v>1.684001120857983</v>
+        <v>1.644825770409983</v>
       </c>
       <c r="E11" t="n">
-        <v>9.905490292989002</v>
+        <v>9.872329251345141</v>
       </c>
       <c r="F11" t="n">
-        <v>0.752983592576414</v>
+        <v>0.7530893958708189</v>
       </c>
       <c r="G11" t="n">
-        <v>26.0145563173199</v>
+        <v>25.45114615158854</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63724525851504</v>
+        <v>34.64211221005767</v>
       </c>
       <c r="I11" t="n">
-        <v>3.238185045574434</v>
+        <v>3.322978808065031</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706147453602588</v>
+        <v>4.706808724192618</v>
       </c>
       <c r="K11" t="n">
-        <v>19.06139091856464</v>
+        <v>19.60670968847019</v>
       </c>
       <c r="L11" t="n">
-        <v>42.5248667149959</v>
+        <v>42.61318724793499</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89220425458389</v>
+        <v>99.88938644320652</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.50210077644212</v>
+        <v>77.91838321289288</v>
       </c>
       <c r="C12" t="n">
-        <v>36.37027094174651</v>
+        <v>35.708008305031</v>
       </c>
       <c r="D12" t="n">
-        <v>1.576694941553771</v>
+        <v>1.536530283787538</v>
       </c>
       <c r="E12" t="n">
-        <v>9.724566722202143</v>
+        <v>9.684406367830398</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538473689214427</v>
+        <v>0.7539825912279314</v>
       </c>
       <c r="G12" t="n">
-        <v>24.35688364113807</v>
+        <v>23.77544024572943</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67697897038637</v>
+        <v>34.68319919648484</v>
       </c>
       <c r="I12" t="n">
-        <v>2.701583076481314</v>
+        <v>2.772433332658148</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711546055759017</v>
+        <v>4.712391195174572</v>
       </c>
       <c r="K12" t="n">
-        <v>21.49789922355789</v>
+        <v>22.08161678710714</v>
       </c>
       <c r="L12" t="n">
-        <v>42.04188025009633</v>
+        <v>42.11806994097115</v>
       </c>
       <c r="M12" t="n">
-        <v>99.91005041540072</v>
+        <v>99.90769503310929</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.12936227143203</v>
+        <v>75.36410010712942</v>
       </c>
       <c r="C13" t="n">
-        <v>34.41447404053885</v>
+        <v>33.58113656790329</v>
       </c>
       <c r="D13" t="n">
-        <v>1.473231875328622</v>
+        <v>1.425840454582959</v>
       </c>
       <c r="E13" t="n">
-        <v>9.462028638211496</v>
+        <v>9.372207224120219</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7545912018014336</v>
+        <v>0.754753848779727</v>
       </c>
       <c r="G13" t="n">
-        <v>22.75857961999501</v>
+        <v>22.06268557513723</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71119528286594</v>
+        <v>34.71867704386744</v>
       </c>
       <c r="I13" t="n">
-        <v>2.253540641970553</v>
+        <v>2.312724405768554</v>
       </c>
       <c r="J13" t="n">
-        <v>4.71619501125896</v>
+        <v>4.717211554873294</v>
       </c>
       <c r="K13" t="n">
-        <v>23.87063772856797</v>
+        <v>24.63589989287057</v>
       </c>
       <c r="L13" t="n">
-        <v>41.63984425654647</v>
+        <v>41.70595150220787</v>
       </c>
       <c r="M13" t="n">
-        <v>99.9249560256533</v>
+        <v>99.92298796298174</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.14850682362137</v>
+        <v>82.58524871326387</v>
       </c>
       <c r="C14" t="n">
-        <v>38.81189875988029</v>
+        <v>38.16200486182599</v>
       </c>
       <c r="D14" t="n">
-        <v>1.474929470610393</v>
+        <v>1.427486530809784</v>
       </c>
       <c r="E14" t="n">
-        <v>11.89670805743143</v>
+        <v>11.89726381379172</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7554607122195124</v>
+        <v>0.7556251821491711</v>
       </c>
       <c r="G14" t="n">
-        <v>24.72952321216636</v>
+        <v>24.12568585540278</v>
       </c>
       <c r="H14" t="n">
-        <v>36.69591179449002</v>
+        <v>36.7962881640882</v>
       </c>
       <c r="I14" t="n">
-        <v>2.874344125331722</v>
+        <v>2.860241778589878</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721629451371952</v>
+        <v>4.722657388432319</v>
       </c>
       <c r="K14" t="n">
-        <v>16.85149317637861</v>
+        <v>17.41475128673613</v>
       </c>
       <c r="L14" t="n">
-        <v>44.24090686874655</v>
+        <v>44.32801239975036</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90429880500545</v>
+        <v>99.90476854831249</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.43233169085036</v>
+        <v>81.7238632775577</v>
       </c>
       <c r="C15" t="n">
-        <v>38.53966078150832</v>
+        <v>37.72026457719651</v>
       </c>
       <c r="D15" t="n">
-        <v>1.448608804599516</v>
+        <v>1.393530507009009</v>
       </c>
       <c r="E15" t="n">
-        <v>12.08400837975351</v>
+        <v>12.03359089524972</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7561931511441373</v>
+        <v>0.7563605086225994</v>
       </c>
       <c r="G15" t="n">
-        <v>24.28821565540143</v>
+        <v>23.57348963398061</v>
       </c>
       <c r="H15" t="n">
-        <v>36.73148944100181</v>
+        <v>36.85378423349552</v>
       </c>
       <c r="I15" t="n">
-        <v>2.397609064299107</v>
+        <v>2.385854320308999</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726207194650859</v>
+        <v>4.727253178891246</v>
       </c>
       <c r="K15" t="n">
-        <v>17.56766830914961</v>
+        <v>18.27613672244228</v>
       </c>
       <c r="L15" t="n">
-        <v>43.81282801697174</v>
+        <v>43.92414753984481</v>
       </c>
       <c r="M15" t="n">
-        <v>99.92015710762968</v>
+        <v>99.92054883948362</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.06528888852611</v>
+        <v>79.03186198512776</v>
       </c>
       <c r="C16" t="n">
-        <v>36.54298444750476</v>
+        <v>35.39633890803044</v>
       </c>
       <c r="D16" t="n">
-        <v>1.359077140890133</v>
+        <v>1.293227834338341</v>
       </c>
       <c r="E16" t="n">
-        <v>11.67043142204618</v>
+        <v>11.4990913339431</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7568226946419541</v>
+        <v>0.7569953020064818</v>
       </c>
       <c r="G16" t="n">
-        <v>22.78707583818103</v>
+        <v>21.87673164944425</v>
       </c>
       <c r="H16" t="n">
-        <v>36.76206902282917</v>
+        <v>36.88471464053786</v>
       </c>
       <c r="I16" t="n">
-        <v>1.999670928425436</v>
+        <v>1.989880587317212</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730141841512213</v>
+        <v>4.731220637540511</v>
       </c>
       <c r="K16" t="n">
-        <v>19.93471111147389</v>
+        <v>20.96813801487225</v>
       </c>
       <c r="L16" t="n">
-        <v>43.45570418923526</v>
+        <v>43.5692493459776</v>
       </c>
       <c r="M16" t="n">
-        <v>99.9333997482139</v>
+        <v>99.93372626888029</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.81108174360301</v>
+        <v>80.93224083371534</v>
       </c>
       <c r="C17" t="n">
-        <v>37.81958800991372</v>
+        <v>36.77618888529213</v>
       </c>
       <c r="D17" t="n">
-        <v>1.360171636677828</v>
+        <v>1.294274358607034</v>
       </c>
       <c r="E17" t="n">
-        <v>12.4681329528149</v>
+        <v>12.34774732119401</v>
       </c>
       <c r="F17" t="n">
-        <v>0.757432181201911</v>
+        <v>0.757607888539033</v>
       </c>
       <c r="G17" t="n">
-        <v>23.26430821515062</v>
+        <v>22.40631986892638</v>
       </c>
       <c r="H17" t="n">
-        <v>37.25055578022609</v>
+        <v>37.42644783402014</v>
       </c>
       <c r="I17" t="n">
-        <v>1.976529845019715</v>
+        <v>1.964794259059787</v>
       </c>
       <c r="J17" t="n">
-        <v>4.733951132511944</v>
+        <v>4.735049303368956</v>
       </c>
       <c r="K17" t="n">
-        <v>18.188918256397</v>
+        <v>19.06775916628466</v>
       </c>
       <c r="L17" t="n">
-        <v>43.92566242097804</v>
+        <v>44.09061176289462</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93416868728876</v>
+        <v>99.9345598144714</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.55659631557063</v>
+        <v>78.33995565560573</v>
       </c>
       <c r="C18" t="n">
-        <v>35.8700775918434</v>
+        <v>34.48655235069293</v>
       </c>
       <c r="D18" t="n">
-        <v>1.278382773470113</v>
+        <v>1.202038764787086</v>
       </c>
       <c r="E18" t="n">
-        <v>11.99311575908128</v>
+        <v>11.74087173145981</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7579552613684094</v>
+        <v>0.7581360642367669</v>
       </c>
       <c r="G18" t="n">
-        <v>21.86539555521714</v>
+        <v>20.80954851617057</v>
       </c>
       <c r="H18" t="n">
-        <v>37.27628089120402</v>
+        <v>37.45254014443227</v>
       </c>
       <c r="I18" t="n">
-        <v>1.648245691677115</v>
+        <v>1.638470033039433</v>
       </c>
       <c r="J18" t="n">
-        <v>4.737220383552558</v>
+        <v>4.738350401479793</v>
       </c>
       <c r="K18" t="n">
-        <v>20.44340368442937</v>
+        <v>21.66004434439428</v>
       </c>
       <c r="L18" t="n">
-        <v>43.63161511692113</v>
+        <v>43.79882568660559</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94509639319389</v>
+        <v>99.94542238169279</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.65762957774591</v>
+        <v>77.30289628570164</v>
       </c>
       <c r="C19" t="n">
-        <v>35.22480562404516</v>
+        <v>33.68925702118809</v>
       </c>
       <c r="D19" t="n">
-        <v>1.246401237825113</v>
+        <v>1.165307599735042</v>
       </c>
       <c r="E19" t="n">
-        <v>11.92213812933132</v>
+        <v>11.61171327881041</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7583967047717641</v>
+        <v>0.7585864408380489</v>
       </c>
       <c r="G19" t="n">
-        <v>21.31838495568988</v>
+        <v>20.17366306588613</v>
       </c>
       <c r="H19" t="n">
-        <v>37.29799110173981</v>
+        <v>37.47478911600258</v>
       </c>
       <c r="I19" t="n">
-        <v>1.374338043564507</v>
+        <v>1.37767152919163</v>
       </c>
       <c r="J19" t="n">
-        <v>4.739979404823525</v>
+        <v>4.741165255237806</v>
       </c>
       <c r="K19" t="n">
-        <v>21.34237042225409</v>
+        <v>22.69710371429835</v>
       </c>
       <c r="L19" t="n">
-        <v>43.38703935115417</v>
+        <v>43.56774414455867</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95421539745342</v>
+        <v>99.95410488004512</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>76.12078369249511</v>
+        <v>74.54837729946526</v>
       </c>
       <c r="C20" t="n">
-        <v>32.89935542619568</v>
+        <v>31.14609466697651</v>
       </c>
       <c r="D20" t="n">
-        <v>1.155295809517009</v>
+        <v>1.06844195271496</v>
       </c>
       <c r="E20" t="n">
-        <v>11.24166808906408</v>
+        <v>10.83793660768301</v>
       </c>
       <c r="F20" t="n">
-        <v>0.758777246350871</v>
+        <v>0.7589760534993251</v>
       </c>
       <c r="G20" t="n">
-        <v>19.76012222834037</v>
+        <v>18.49673679673068</v>
       </c>
       <c r="H20" t="n">
-        <v>37.31670615725372</v>
+        <v>37.49403629935865</v>
       </c>
       <c r="I20" t="n">
-        <v>1.145856372276115</v>
+        <v>1.148649255107845</v>
       </c>
       <c r="J20" t="n">
-        <v>4.742357789692942</v>
+        <v>4.743600334370782</v>
       </c>
       <c r="K20" t="n">
-        <v>23.87921630750489</v>
+        <v>25.45162270053475</v>
       </c>
       <c r="L20" t="n">
-        <v>43.18325220953376</v>
+        <v>43.36401397890007</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96182394323432</v>
+        <v>99.96173134641134</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.78652823351977</v>
+        <v>81.0140695048643</v>
       </c>
       <c r="C21" t="n">
-        <v>36.438227380729</v>
+        <v>35.24822523812928</v>
       </c>
       <c r="D21" t="n">
-        <v>1.156053671850512</v>
+        <v>1.069129642650391</v>
       </c>
       <c r="E21" t="n">
-        <v>13.14550766308411</v>
+        <v>13.01965357787369</v>
       </c>
       <c r="F21" t="n">
-        <v>0.75927499652861</v>
+        <v>0.7594645593951276</v>
       </c>
       <c r="G21" t="n">
-        <v>21.40129415685429</v>
+        <v>20.42266455850265</v>
       </c>
       <c r="H21" t="n">
-        <v>38.96939502675809</v>
+        <v>39.43219144665691</v>
       </c>
       <c r="I21" t="n">
-        <v>1.609533990140361</v>
+        <v>1.564312223565996</v>
       </c>
       <c r="J21" t="n">
-        <v>4.745468728303811</v>
+        <v>4.746653496219547</v>
       </c>
       <c r="K21" t="n">
-        <v>18.21347176648021</v>
+        <v>18.98593049513568</v>
       </c>
       <c r="L21" t="n">
-        <v>45.29468489131304</v>
+        <v>45.71373406605944</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94638403852225</v>
+        <v>99.9478897993244</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_31_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_31_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.46159234493989</v>
+        <v>43.57420404826062</v>
       </c>
       <c r="M2" t="n">
-        <v>100.2823565104848</v>
+        <v>96.98248136770417</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.98650215651612</v>
+        <v>81.57353375530896</v>
       </c>
       <c r="C3" t="n">
-        <v>45.92695512925926</v>
+        <v>43.3290893108645</v>
       </c>
       <c r="D3" t="n">
-        <v>2.22862720405282</v>
+        <v>2.185571565176471</v>
       </c>
       <c r="E3" t="n">
-        <v>5.703058544360479</v>
+        <v>4.156984740631997</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428757346842735</v>
+        <v>0.7377011057759837</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97296418372759</v>
+        <v>32.87463895952941</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17228379547657</v>
+        <v>33.93425086569525</v>
       </c>
       <c r="I3" t="n">
-        <v>6.523719352437683</v>
+        <v>3.073754607399932</v>
       </c>
       <c r="J3" t="n">
-        <v>4.642973341776709</v>
+        <v>4.610631911099897</v>
       </c>
       <c r="K3" t="n">
-        <v>12.01349784348387</v>
+        <v>18.42646624469105</v>
       </c>
       <c r="L3" t="n">
-        <v>48.82536809089375</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7658210636369</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>86.99453694551691</v>
+        <v>88.64009901148714</v>
       </c>
       <c r="C4" t="n">
-        <v>42.56163258810897</v>
+        <v>42.90960129477082</v>
       </c>
       <c r="D4" t="n">
-        <v>2.180413150328158</v>
+        <v>2.191301823682763</v>
       </c>
       <c r="E4" t="n">
-        <v>6.48764221814868</v>
+        <v>6.530187860820289</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444264160345901</v>
+        <v>0.7396352533938551</v>
       </c>
       <c r="G4" t="n">
-        <v>33.23799410108587</v>
+        <v>33.56097924249829</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24361513759114</v>
+        <v>34.02322165611733</v>
       </c>
       <c r="I4" t="n">
-        <v>5.447780822112297</v>
+        <v>6.972052841263016</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652665100216188</v>
+        <v>4.622720333711594</v>
       </c>
       <c r="K4" t="n">
-        <v>13.00546305448308</v>
+        <v>11.35990098851286</v>
       </c>
       <c r="L4" t="n">
-        <v>44.25168993095135</v>
+        <v>45.49870368639627</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81878557354339</v>
+        <v>99.76820596967995</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.68864042642079</v>
+        <v>87.41297469052648</v>
       </c>
       <c r="C5" t="n">
-        <v>42.10121559179454</v>
+        <v>42.76332053183219</v>
       </c>
       <c r="D5" t="n">
-        <v>2.116203306779816</v>
+        <v>2.132430245788841</v>
       </c>
       <c r="E5" t="n">
-        <v>7.054565862916278</v>
+        <v>7.325238492642355</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457434085200632</v>
+        <v>0.7412775936666253</v>
       </c>
       <c r="G5" t="n">
-        <v>32.25918584138967</v>
+        <v>32.65932900777596</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30419679192291</v>
+        <v>34.09876930866476</v>
       </c>
       <c r="I5" t="n">
-        <v>4.547848911641662</v>
+        <v>5.822945081571545</v>
       </c>
       <c r="J5" t="n">
-        <v>4.660896303250395</v>
+        <v>4.632984960416407</v>
       </c>
       <c r="K5" t="n">
-        <v>14.3113595735792</v>
+        <v>12.58702530947352</v>
       </c>
       <c r="L5" t="n">
-        <v>43.43609758956758</v>
+        <v>44.45598602421477</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84867275494133</v>
+        <v>99.80633186552046</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.15872966871517</v>
+        <v>85.96685320101901</v>
       </c>
       <c r="C6" t="n">
-        <v>41.27743334407266</v>
+        <v>42.22089622280679</v>
       </c>
       <c r="D6" t="n">
-        <v>2.041120787132509</v>
+        <v>2.06309326715709</v>
       </c>
       <c r="E6" t="n">
-        <v>7.436866371184498</v>
+        <v>7.897321803295879</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468645132392348</v>
+        <v>0.7426749524872912</v>
       </c>
       <c r="G6" t="n">
-        <v>31.11463562403463</v>
+        <v>31.59739546879551</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35576760900479</v>
+        <v>34.16304781441539</v>
       </c>
       <c r="I6" t="n">
-        <v>3.795571556374286</v>
+        <v>4.861601441822273</v>
       </c>
       <c r="J6" t="n">
-        <v>4.667903207745217</v>
+        <v>4.64171845304557</v>
       </c>
       <c r="K6" t="n">
-        <v>15.84127033128481</v>
+        <v>14.03314679898099</v>
       </c>
       <c r="L6" t="n">
-        <v>42.75496718820802</v>
+        <v>43.58420850372412</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87367086356551</v>
+        <v>99.83825152551191</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.38740335956614</v>
+        <v>84.31646775728723</v>
       </c>
       <c r="C7" t="n">
-        <v>40.09532370260493</v>
+        <v>41.32532247047931</v>
       </c>
       <c r="D7" t="n">
-        <v>1.954554377910416</v>
+        <v>1.984339833276607</v>
       </c>
       <c r="E7" t="n">
-        <v>7.649298044262177</v>
+        <v>8.272166882717784</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478215129841338</v>
+        <v>0.7438663573389417</v>
       </c>
       <c r="G7" t="n">
-        <v>29.79502617357656</v>
+        <v>30.39124379622656</v>
       </c>
       <c r="H7" t="n">
-        <v>34.39978959727015</v>
+        <v>34.21785243759131</v>
       </c>
       <c r="I7" t="n">
-        <v>3.16702919741188</v>
+        <v>4.057833716767639</v>
       </c>
       <c r="J7" t="n">
-        <v>4.673884456150836</v>
+        <v>4.649164733368385</v>
       </c>
       <c r="K7" t="n">
-        <v>17.61259664043386</v>
+        <v>15.68353224271277</v>
       </c>
       <c r="L7" t="n">
-        <v>42.18664711372858</v>
+        <v>42.85610080231286</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89456745676736</v>
+        <v>99.86495551550493</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.40878337200284</v>
+        <v>82.48668322357761</v>
       </c>
       <c r="C8" t="n">
-        <v>42.44310344583199</v>
+        <v>40.12542035206803</v>
       </c>
       <c r="D8" t="n">
-        <v>1.958813690682298</v>
+        <v>1.897606573291739</v>
       </c>
       <c r="E8" t="n">
-        <v>9.51770373840483</v>
+        <v>8.474958991741387</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494511456806396</v>
+        <v>0.7448842375915351</v>
       </c>
       <c r="G8" t="n">
-        <v>30.30962575012506</v>
+        <v>29.06287674677361</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47475270130942</v>
+        <v>34.26467492921061</v>
       </c>
       <c r="I8" t="n">
-        <v>5.714366685296601</v>
+        <v>3.386155260021656</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684069660503998</v>
+        <v>4.655526484947094</v>
       </c>
       <c r="K8" t="n">
-        <v>12.59121662799715</v>
+        <v>17.51331677642236</v>
       </c>
       <c r="L8" t="n">
-        <v>44.77561522059829</v>
+        <v>42.24854526826606</v>
       </c>
       <c r="M8" t="n">
-        <v>99.80993529442743</v>
+        <v>99.88728239675646</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.19938211038469</v>
+        <v>80.54312494925404</v>
       </c>
       <c r="C9" t="n">
-        <v>41.11985510289921</v>
+        <v>38.70706761674437</v>
       </c>
       <c r="D9" t="n">
-        <v>1.858706241243879</v>
+        <v>1.806193183853537</v>
       </c>
       <c r="E9" t="n">
-        <v>9.826433878538857</v>
+        <v>8.537544054671821</v>
       </c>
       <c r="F9" t="n">
-        <v>0.750850031806183</v>
+        <v>0.7457551453297593</v>
       </c>
       <c r="G9" t="n">
-        <v>28.76061711203393</v>
+        <v>27.66283096929788</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53910146308441</v>
+        <v>34.30473668516892</v>
       </c>
       <c r="I9" t="n">
-        <v>4.770860684888786</v>
+        <v>2.825095252621121</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692812698788644</v>
+        <v>4.660969658310995</v>
       </c>
       <c r="K9" t="n">
-        <v>14.8006178896153</v>
+        <v>19.45687505074595</v>
       </c>
       <c r="L9" t="n">
-        <v>43.92079459956059</v>
+        <v>41.74199746417575</v>
       </c>
       <c r="M9" t="n">
-        <v>99.8412675920751</v>
+        <v>99.90594013166607</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>82.83438129197826</v>
+        <v>85.56968319435784</v>
       </c>
       <c r="C10" t="n">
-        <v>39.49422598478428</v>
+        <v>42.15467208241928</v>
       </c>
       <c r="D10" t="n">
-        <v>1.752825659474122</v>
+        <v>1.808230818984932</v>
       </c>
       <c r="E10" t="n">
-        <v>9.930355687268875</v>
+        <v>10.49160513047342</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520532161555974</v>
+        <v>0.7465964600335945</v>
       </c>
       <c r="G10" t="n">
-        <v>27.12227814038368</v>
+        <v>29.15579595957234</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59444794315748</v>
+        <v>35.80519466154646</v>
       </c>
       <c r="I10" t="n">
-        <v>3.982088044566027</v>
+        <v>2.896032288537124</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700332600972484</v>
+        <v>4.666227875209965</v>
       </c>
       <c r="K10" t="n">
-        <v>17.16561870802175</v>
+        <v>14.43031680564217</v>
       </c>
       <c r="L10" t="n">
-        <v>43.20763139928038</v>
+        <v>43.31858548373414</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86747609208641</v>
+        <v>99.90357437179559</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>80.3932903115298</v>
+        <v>85.20965667625643</v>
       </c>
       <c r="C11" t="n">
-        <v>37.66948950680134</v>
+        <v>42.14153430789901</v>
       </c>
       <c r="D11" t="n">
-        <v>1.644825770409983</v>
+        <v>1.785204714622417</v>
       </c>
       <c r="E11" t="n">
-        <v>9.872329251345141</v>
+        <v>10.81735346694161</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530893958708189</v>
+        <v>0.7473175823095239</v>
       </c>
       <c r="G11" t="n">
-        <v>25.45114615158854</v>
+        <v>28.83236219152187</v>
       </c>
       <c r="H11" t="n">
-        <v>34.64211221005767</v>
+        <v>35.88761580701642</v>
       </c>
       <c r="I11" t="n">
-        <v>3.322978808065031</v>
+        <v>2.46906802441007</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706808724192618</v>
+        <v>4.670734889434524</v>
       </c>
       <c r="K11" t="n">
-        <v>19.60670968847019</v>
+        <v>14.79034332374356</v>
       </c>
       <c r="L11" t="n">
-        <v>42.61318724793499</v>
+        <v>42.9858995182491</v>
       </c>
       <c r="M11" t="n">
-        <v>99.88938644320652</v>
+        <v>99.91777714989168</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>77.91838321289288</v>
+        <v>83.2717750653666</v>
       </c>
       <c r="C12" t="n">
-        <v>35.708008305031</v>
+        <v>40.58728245900699</v>
       </c>
       <c r="D12" t="n">
-        <v>1.536530283787538</v>
+        <v>1.703114704287638</v>
       </c>
       <c r="E12" t="n">
-        <v>9.684406367830398</v>
+        <v>10.6631421867547</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539825912279314</v>
+        <v>0.7479336036791018</v>
       </c>
       <c r="G12" t="n">
-        <v>23.77544024572943</v>
+        <v>27.5065484678119</v>
       </c>
       <c r="H12" t="n">
-        <v>34.68319919648484</v>
+        <v>35.9171983282412</v>
       </c>
       <c r="I12" t="n">
-        <v>2.772433332658148</v>
+        <v>2.059252751597689</v>
       </c>
       <c r="J12" t="n">
-        <v>4.712391195174572</v>
+        <v>4.674585022994385</v>
       </c>
       <c r="K12" t="n">
-        <v>22.08161678710714</v>
+        <v>16.72822493463338</v>
       </c>
       <c r="L12" t="n">
-        <v>42.11806994097115</v>
+        <v>42.61590738345934</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90769503310929</v>
+        <v>99.93141477709972</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>75.36410010712942</v>
+        <v>84.51184022555485</v>
       </c>
       <c r="C13" t="n">
-        <v>33.58113656790329</v>
+        <v>41.61262507015915</v>
       </c>
       <c r="D13" t="n">
-        <v>1.425840454582959</v>
+        <v>1.704396573967915</v>
       </c>
       <c r="E13" t="n">
-        <v>9.372207224120219</v>
+        <v>11.32650638157216</v>
       </c>
       <c r="F13" t="n">
-        <v>0.754753848779727</v>
+        <v>0.7484965448638636</v>
       </c>
       <c r="G13" t="n">
-        <v>22.06268557513723</v>
+        <v>27.864545810406</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71867704386744</v>
+        <v>36.28152604718657</v>
       </c>
       <c r="I13" t="n">
-        <v>2.312724405768554</v>
+        <v>1.908265462159196</v>
       </c>
       <c r="J13" t="n">
-        <v>4.717211554873294</v>
+        <v>4.678103405399147</v>
       </c>
       <c r="K13" t="n">
-        <v>24.63589989287057</v>
+        <v>15.48815977444515</v>
       </c>
       <c r="L13" t="n">
-        <v>41.70595150220787</v>
+        <v>42.83565414661158</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92298796298174</v>
+        <v>99.93643899121588</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>82.58524871326387</v>
+        <v>82.55822119896594</v>
       </c>
       <c r="C14" t="n">
-        <v>38.16200486182599</v>
+        <v>39.95536315396538</v>
       </c>
       <c r="D14" t="n">
-        <v>1.427486530809784</v>
+        <v>1.624018457349532</v>
       </c>
       <c r="E14" t="n">
-        <v>11.89726381379172</v>
+        <v>11.05756363547592</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7556251821491711</v>
+        <v>0.7489774337000185</v>
       </c>
       <c r="G14" t="n">
-        <v>24.12568585540278</v>
+        <v>26.55047387029821</v>
       </c>
       <c r="H14" t="n">
-        <v>36.7962881640882</v>
+        <v>36.30483594882136</v>
       </c>
       <c r="I14" t="n">
-        <v>2.860241778589878</v>
+        <v>1.59124289269579</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722657388432319</v>
+        <v>4.681108960625116</v>
       </c>
       <c r="K14" t="n">
-        <v>17.41475128673613</v>
+        <v>17.44177880103405</v>
       </c>
       <c r="L14" t="n">
-        <v>44.32801239975036</v>
+        <v>42.54985067105171</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90476854831249</v>
+        <v>99.94699262605114</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>81.7238632775577</v>
+        <v>81.68383742365558</v>
       </c>
       <c r="C15" t="n">
-        <v>37.72026457719651</v>
+        <v>39.30581060158189</v>
       </c>
       <c r="D15" t="n">
-        <v>1.393530507009009</v>
+        <v>1.587645857437203</v>
       </c>
       <c r="E15" t="n">
-        <v>12.03359089524972</v>
+        <v>11.03456391366092</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7563605086225994</v>
+        <v>0.7493894121671992</v>
       </c>
       <c r="G15" t="n">
-        <v>23.57348963398061</v>
+        <v>25.9558317594301</v>
       </c>
       <c r="H15" t="n">
-        <v>36.85378423349552</v>
+        <v>36.32480559008486</v>
       </c>
       <c r="I15" t="n">
-        <v>2.385854320308999</v>
+        <v>1.347917064830295</v>
       </c>
       <c r="J15" t="n">
-        <v>4.727253178891246</v>
+        <v>4.683683826044995</v>
       </c>
       <c r="K15" t="n">
-        <v>18.27613672244228</v>
+        <v>18.31616257634442</v>
       </c>
       <c r="L15" t="n">
-        <v>43.92414753984481</v>
+        <v>42.33312095392441</v>
       </c>
       <c r="M15" t="n">
-        <v>99.92054883948362</v>
+        <v>99.95509413185073</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>79.03186198512776</v>
+        <v>79.33689099683724</v>
       </c>
       <c r="C16" t="n">
-        <v>35.39633890803044</v>
+        <v>37.16769521932574</v>
       </c>
       <c r="D16" t="n">
-        <v>1.293227834338341</v>
+        <v>1.491763332402704</v>
       </c>
       <c r="E16" t="n">
-        <v>11.4990913339431</v>
+        <v>10.55545378246428</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7569953020064818</v>
+        <v>0.7497432449391351</v>
       </c>
       <c r="G16" t="n">
-        <v>21.87673164944425</v>
+        <v>24.38828401141902</v>
       </c>
       <c r="H16" t="n">
-        <v>36.88471464053786</v>
+        <v>36.34195676201669</v>
       </c>
       <c r="I16" t="n">
-        <v>1.989880587317212</v>
+        <v>1.123794582725818</v>
       </c>
       <c r="J16" t="n">
-        <v>4.731220637540511</v>
+        <v>4.685895280869595</v>
       </c>
       <c r="K16" t="n">
-        <v>20.96813801487225</v>
+        <v>20.66310900316276</v>
       </c>
       <c r="L16" t="n">
-        <v>43.5692493459776</v>
+        <v>42.13175363682177</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93372626888029</v>
+        <v>99.96255785931027</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>80.93224083371534</v>
+        <v>84.17994077918014</v>
       </c>
       <c r="C17" t="n">
-        <v>36.77618888529213</v>
+        <v>40.36199174144768</v>
       </c>
       <c r="D17" t="n">
-        <v>1.294274358607034</v>
+        <v>1.49251093108961</v>
       </c>
       <c r="E17" t="n">
-        <v>12.34774732119401</v>
+        <v>12.2553805127738</v>
       </c>
       <c r="F17" t="n">
-        <v>0.757607888539033</v>
+        <v>0.7501189795166371</v>
       </c>
       <c r="G17" t="n">
-        <v>22.40631986892638</v>
+        <v>25.88420877062087</v>
       </c>
       <c r="H17" t="n">
-        <v>37.42644783402014</v>
+        <v>37.84387211628005</v>
       </c>
       <c r="I17" t="n">
-        <v>1.964794259059787</v>
+        <v>1.265605846920188</v>
       </c>
       <c r="J17" t="n">
-        <v>4.735049303368956</v>
+        <v>4.688243621978982</v>
       </c>
       <c r="K17" t="n">
-        <v>19.06775916628466</v>
+        <v>15.82005922081987</v>
       </c>
       <c r="L17" t="n">
-        <v>44.09061176289462</v>
+        <v>43.77578330756631</v>
       </c>
       <c r="M17" t="n">
-        <v>99.9345598144714</v>
+        <v>99.95783426983385</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>78.33995565560573</v>
+        <v>85.83099498079719</v>
       </c>
       <c r="C18" t="n">
-        <v>34.48655235069293</v>
+        <v>41.11247470640937</v>
       </c>
       <c r="D18" t="n">
-        <v>1.202038764787086</v>
+        <v>1.493738368102852</v>
       </c>
       <c r="E18" t="n">
-        <v>11.74087173145981</v>
+        <v>12.87034198944201</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7581360642367669</v>
+        <v>0.7507358753668553</v>
       </c>
       <c r="G18" t="n">
-        <v>20.80954851617057</v>
+        <v>26.03146926316055</v>
       </c>
       <c r="H18" t="n">
-        <v>37.45254014443227</v>
+        <v>37.87499481588134</v>
       </c>
       <c r="I18" t="n">
-        <v>1.638470033039433</v>
+        <v>2.117615447800742</v>
       </c>
       <c r="J18" t="n">
-        <v>4.738350401479793</v>
+        <v>4.692099221042845</v>
       </c>
       <c r="K18" t="n">
-        <v>21.66004434439428</v>
+        <v>14.16900501920279</v>
       </c>
       <c r="L18" t="n">
-        <v>43.79882568660559</v>
+        <v>44.64799109580304</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94542238169279</v>
+        <v>99.92947082141522</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>77.30289628570164</v>
+        <v>83.13286758269275</v>
       </c>
       <c r="C19" t="n">
-        <v>33.68925702118809</v>
+        <v>38.74227135460679</v>
       </c>
       <c r="D19" t="n">
-        <v>1.165307599735042</v>
+        <v>1.394954598801678</v>
       </c>
       <c r="E19" t="n">
-        <v>11.61171327881041</v>
+        <v>12.31352321961925</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7585864408380489</v>
+        <v>0.7512674526443609</v>
       </c>
       <c r="G19" t="n">
-        <v>20.17366306588613</v>
+        <v>24.30995851591462</v>
       </c>
       <c r="H19" t="n">
-        <v>37.47478911600258</v>
+        <v>37.90181315145099</v>
       </c>
       <c r="I19" t="n">
-        <v>1.37767152919163</v>
+        <v>1.765929065234608</v>
       </c>
       <c r="J19" t="n">
-        <v>4.741165255237806</v>
+        <v>4.695421579027256</v>
       </c>
       <c r="K19" t="n">
-        <v>22.69710371429835</v>
+        <v>16.86713241730726</v>
       </c>
       <c r="L19" t="n">
-        <v>43.56774414455867</v>
+        <v>44.33177357675813</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95410488004512</v>
+        <v>99.94117734867217</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>74.54837729946526</v>
+        <v>80.42420603172172</v>
       </c>
       <c r="C20" t="n">
-        <v>31.14609466697651</v>
+        <v>36.30631016173589</v>
       </c>
       <c r="D20" t="n">
-        <v>1.06844195271496</v>
+        <v>1.296360358451875</v>
       </c>
       <c r="E20" t="n">
-        <v>10.83793660768301</v>
+        <v>11.68863117050508</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7589760534993251</v>
+        <v>0.7517259570556558</v>
       </c>
       <c r="G20" t="n">
-        <v>18.49673679673068</v>
+        <v>22.59175070121528</v>
       </c>
       <c r="H20" t="n">
-        <v>37.49403629935865</v>
+        <v>37.92494492491575</v>
       </c>
       <c r="I20" t="n">
-        <v>1.148649255107845</v>
+        <v>1.472505687980227</v>
       </c>
       <c r="J20" t="n">
-        <v>4.743600334370782</v>
+        <v>4.698287231597849</v>
       </c>
       <c r="K20" t="n">
-        <v>25.45162270053475</v>
+        <v>19.57579396827829</v>
       </c>
       <c r="L20" t="n">
-        <v>43.36401397890007</v>
+        <v>44.06884228484042</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96173134641134</v>
+        <v>99.95094641485461</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.0140695048643</v>
+        <v>77.73061430801084</v>
       </c>
       <c r="C21" t="n">
-        <v>35.24822523812928</v>
+        <v>33.83939114240319</v>
       </c>
       <c r="D21" t="n">
-        <v>1.069129642650391</v>
+        <v>1.198840972520289</v>
       </c>
       <c r="E21" t="n">
-        <v>13.01965357787369</v>
+        <v>11.0139701318441</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7594645593951276</v>
+        <v>0.7521217340253524</v>
       </c>
       <c r="G21" t="n">
-        <v>20.42266455850265</v>
+        <v>20.89227443974351</v>
       </c>
       <c r="H21" t="n">
-        <v>39.43219144665691</v>
+        <v>37.94491206804472</v>
       </c>
       <c r="I21" t="n">
-        <v>1.564312223565996</v>
+        <v>1.227734124174419</v>
       </c>
       <c r="J21" t="n">
-        <v>4.746653496219547</v>
+        <v>4.700760837658453</v>
       </c>
       <c r="K21" t="n">
-        <v>18.98593049513568</v>
+        <v>22.26938569198914</v>
       </c>
       <c r="L21" t="n">
-        <v>45.71373406605944</v>
+        <v>43.85032022983046</v>
       </c>
       <c r="M21" t="n">
-        <v>99.9478897993244</v>
+        <v>99.95909706422279</v>
       </c>
     </row>
   </sheetData>
